--- a/data/trans_orig/Q20C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización</t>
+          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 19,25</t>
+          <t>5,48; 17,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,02</t>
+          <t>3,33; 8,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 31,37</t>
+          <t>3,25; 35,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 14,2</t>
+          <t>4,85; 14,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,76</t>
+          <t>4,04; 7,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,78</t>
+          <t>3,47; 6,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,45</t>
+          <t>3,46; 8,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,91</t>
+          <t>3,95; 10,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,7</t>
+          <t>4,95; 10,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,44</t>
+          <t>3,75; 6,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 16,38</t>
+          <t>4,03; 15,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,15</t>
+          <t>4,94; 10,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,5</t>
+          <t>1,4; 3,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,2</t>
+          <t>3,97; 9,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,28</t>
+          <t>5,55; 11,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,76</t>
+          <t>4,07; 11,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,21</t>
+          <t>1,84; 5,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,58</t>
+          <t>4,2; 8,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,56</t>
+          <t>5,44; 9,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,78</t>
+          <t>3,82; 12,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,43</t>
+          <t>2,02; 4,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,02</t>
+          <t>4,61; 8,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,68</t>
+          <t>5,91; 9,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,06</t>
+          <t>4,64; 9,83</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,42</t>
+          <t>3,47; 14,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,89</t>
+          <t>2,02; 5,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,17</t>
+          <t>3,83; 10,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,9</t>
+          <t>4,15; 12,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,95</t>
+          <t>2,84; 9,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,99</t>
+          <t>2,87; 11,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,31</t>
+          <t>3,78; 10,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,06</t>
+          <t>2,4; 5,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,77</t>
+          <t>3,99; 9,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,93</t>
+          <t>4,97; 11,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,64</t>
+          <t>4,13; 7,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,64</t>
+          <t>5,52; 13,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,62</t>
+          <t>5,24; 10,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,43; 5,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,96</t>
+          <t>4,43; 6,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,18</t>
+          <t>4,89; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,02</t>
+          <t>4,35; 9,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,61</t>
+          <t>4,39; 7,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,64</t>
+          <t>4,56; 6,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,91</t>
+          <t>5,83; 10,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,65</t>
+          <t>5,2; 8,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 17,52</t>
+          <t>5,7; 19,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,31</t>
+          <t>3,18; 7,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 35,18</t>
+          <t>3,16; 36,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,04</t>
+          <t>4,91; 13,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,94</t>
+          <t>4,09; 7,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,67</t>
+          <t>3,46; 6,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,06</t>
+          <t>3,47; 8,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,03</t>
+          <t>4,15; 10,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,64</t>
+          <t>5,18; 10,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,47</t>
+          <t>3,78; 6,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 15,98</t>
+          <t>4,15; 16,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,79</t>
+          <t>5,0; 10,21</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>7,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,54</t>
+          <t>1,44; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,83</t>
+          <t>4,19; 9,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,38</t>
+          <t>5,65; 11,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,66</t>
+          <t>4,93; 12,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,04</t>
+          <t>1,84; 5,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,83</t>
+          <t>4,11; 8,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,71</t>
+          <t>5,43; 10,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 12,46</t>
+          <t>4,19; 12,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,39</t>
+          <t>2,02; 4,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,08</t>
+          <t>4,51; 7,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,69</t>
+          <t>6,07; 9,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,83</t>
+          <t>4,97; 10,2</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,89</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 14,07</t>
+          <t>3,3; 13,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,17</t>
+          <t>1,69; 4,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,94</t>
+          <t>3,87; 10,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,28</t>
+          <t>4,14; 11,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,98</t>
+          <t>3,24; 10,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,21</t>
+          <t>2,77; 10,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,52</t>
+          <t>3,49; 10,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,06</t>
+          <t>2,44; 5,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,05</t>
+          <t>4,2; 9,22</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,87</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,96</t>
+          <t>4,87; 12,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,8</t>
+          <t>4,05; 7,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,84</t>
+          <t>5,33; 14,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,0</t>
+          <t>5,57; 10,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,95</t>
+          <t>3,41; 6,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,99</t>
+          <t>4,41; 6,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,87</t>
+          <t>4,92; 8,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,3</t>
+          <t>4,64; 9,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,92</t>
+          <t>4,36; 7,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,7</t>
+          <t>4,61; 6,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,25</t>
+          <t>5,74; 9,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,55</t>
+          <t>5,42; 8,78</t>
         </is>
       </c>
     </row>
